--- a/PMR_Historico.xlsx
+++ b/PMR_Historico.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -519,7 +519,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ciclo I-2026</t>
+          <t>Segundo período enero-diciembre 2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -541,14 +546,401 @@
       <c r="G4" t="n">
         <v>0.77</v>
       </c>
+      <c r="I4" t="n">
+        <v>2.2</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ALERTA</t>
+          <t>Alerta</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ALERTA</t>
+          <t>Alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Alerta</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Alerta</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Alerta</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Problema</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2020</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Alerta</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2019</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Alerta</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2018</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2017</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>SATISFACTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2016</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SATISFACTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2015</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Desde la Aprobación hasta la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Problema</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>PROBLEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Desde la Aprobación hasta la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>SATISFACTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2013</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Desde la Aprobación hasta la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>SATISFACTORY</t>
         </is>
       </c>
     </row>

--- a/PMR_Historico.xlsx
+++ b/PMR_Historico.xlsx
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1152,7 +1152,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ciclo I-2026</t>
+          <t>Segundo período enero-diciembre 2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Después del proyecto alcanza el 95% de los desembolsos totales</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1174,12 +1179,251 @@
       <c r="G4" t="n">
         <v>0.97</v>
       </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>SATISFACTORIO</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2020</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2019</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Alerta</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SATISFACTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2018</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>SATISFACTORIO</t>
         </is>

--- a/PMR_Historico.xlsx
+++ b/PMR_Historico.xlsx
@@ -1443,7 +1443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1526,7 +1526,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ciclo I-2026</t>
+          <t>Segundo período enero-diciembre 2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1544,6 +1549,9 @@
       <c r="G4" t="n">
         <v>0.6500000000000019</v>
       </c>
+      <c r="I4" t="n">
+        <v>2.85</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>SATISFACTORIO</t>
@@ -1551,7 +1559,224 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SATISFACTORIO</t>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2020</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2019</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Desde la Aprobación hasta la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
         </is>
       </c>
     </row>

--- a/PMR_Historico.xlsx
+++ b/PMR_Historico.xlsx
@@ -1794,7 +1794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1877,7 +1877,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ciclo I-2026</t>
+          <t>Segundo período enero-diciembre 2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1895,6 +1900,9 @@
       <c r="G4" t="n">
         <v>0.04</v>
       </c>
+      <c r="I4" t="n">
+        <v>2.9</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>SATISFACTORIO</t>
@@ -1902,7 +1910,49 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SATISFACTORIO</t>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Desde la Aprobación hasta la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
         </is>
       </c>
     </row>

--- a/PMR_Historico.xlsx
+++ b/PMR_Historico.xlsx
@@ -1970,7 +1970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2053,7 +2053,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ciclo I-2026</t>
+          <t>Segundo período enero-diciembre 2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2075,14 +2080,197 @@
       <c r="G4" t="n">
         <v>0.65</v>
       </c>
+      <c r="I4" t="n">
+        <v>2.4</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ALERTA</t>
+          <t>Alerta</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SATISFACTORIO</t>
+          <t>SATISFACTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Alerta</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2020</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Desde la Aprobación hasta la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2019</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Desde la Aprobación hasta la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
         </is>
       </c>
     </row>

--- a/PMR_Historico.xlsx
+++ b/PMR_Historico.xlsx
@@ -2288,7 +2288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2371,7 +2371,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ciclo I-2026</t>
+          <t>Segundo período enero-diciembre 2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2389,14 +2394,79 @@
       <c r="G4" t="n">
         <v>0.3800000000000001</v>
       </c>
+      <c r="I4" t="n">
+        <v>1.8</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>PROBLEMA</t>
+          <t>Problema</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>PROBLEMA</t>
+          <t>Problem</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Desde la Aprobación hasta la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
         </is>
       </c>
     </row>

--- a/PMR_Historico.xlsx
+++ b/PMR_Historico.xlsx
@@ -2484,7 +2484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2567,7 +2567,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ciclo I-2026</t>
+          <t>Segundo período enero-diciembre 2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Después del proyecto alcanza el 95% de los desembolsos totales</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2589,6 +2594,12 @@
       <c r="G4" t="n">
         <v>1</v>
       </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>SATISFACTORIO</t>
@@ -2596,7 +2607,347 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SATISFACTORIO</t>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Alerta</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SATISFACTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Alerta</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SATISFACTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Problema</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ALERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2020</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2019</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2018</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2017</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Después de la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>SATISFACTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2016</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Desde la Aprobación hasta la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SATISFACTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2015</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Desde la Aprobación hasta la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>SATISFACTORY</t>
         </is>
       </c>
     </row>

--- a/PMR_Historico.xlsx
+++ b/PMR_Historico.xlsx
@@ -2965,7 +2965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3048,17 +3048,44 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ciclo I-2026</t>
+          <t>Segundo período enero-diciembre 2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Desde la Aprobación hasta la Elegibilidad</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ALERTA</t>
+          <t>Alerta</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SATISFACTORIO</t>
+          <t>SATISFACTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Segundo período enero-diciembre 2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Desde la Aprobación hasta la Elegibilidad</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SATISFACTORIO</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Satisfactory</t>
         </is>
       </c>
     </row>

--- a/PMR_Historico.xlsx
+++ b/PMR_Historico.xlsx
@@ -1041,7 +1041,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ciclo I-2026</t>
+          <t>Segundo período enero-diciembre 2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Desde la Aprobación hasta la Elegibilidad</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1051,7 +1056,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SATISFACTORIO</t>
+          <t>Satisfactory</t>
         </is>
       </c>
     </row>

--- a/PMR_Historico.xlsx
+++ b/PMR_Historico.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Alerta</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Alerta</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Alerta</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Alerta</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Problem</t>
+          <t>Problema</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Alerta</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Alerta</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>SATISFACTORY</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>SATISFACTORY</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>PROBLEM</t>
+          <t>Problema</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>SATISFACTORY</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>SATISFACTORY</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SATISFACTORY</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SATISFACTORY</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Alerta</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Problem</t>
+          <t>Problema</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SATISFACTORY</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SATISFACTORY</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ALERT</t>
+          <t>Alerta</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>SATISFACTORY</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>SATISFACTORY</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>SATISFACTORY</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SATISFACTORY</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Satisfactorio</t>
         </is>
       </c>
     </row>

--- a/PMR_Historico.xlsx
+++ b/PMR_Historico.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CR-L1032" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CR-L1065" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CR-L1139" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CR-L1151" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="CR-L1137" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="CR-J0002" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="CR-L1066" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="CR-L1152" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="CR-L1156" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="CR-L1157" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CR-L1032" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CR-L1065" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CR-L1139" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CR-L1151" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CR-L1137" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CR-J0002" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CR-L1066" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CR-L1152" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CR-L1156" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CR-L1157" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -65,12 +65,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -450,6 +453,8 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -515,6 +520,16 @@
           <t>Clasificación Validada</t>
         </is>
       </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Comentarios de simulación PMR</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Plan Acción 2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -557,6 +572,16 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>Alerta</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantiene como meta física finalizar Barranca-Limonal y 18km de ruta 35, así como una meta financiera de $113m para el 2026. Esto genera una alta probabilidad de que la operación finalice con una clasificación de problema (ningún sub-indicador estaría satisfactorio: ni desembolsos, ni metas físicas ni metas financieras planeadas para el año). </t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Asegurar la finalización de pagos de obras complementarias y expropiaciones, así como gastos de ruta 35 con cargo a la operación.</t>
         </is>
       </c>
     </row>
@@ -958,7 +983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -972,6 +997,8 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1037,6 +1064,16 @@
           <t>Clasificación Validada</t>
         </is>
       </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Comentarios de simulación PMR</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Plan Acción 2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1057,6 +1094,16 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>Satisfactorio</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recién se firmó, por lo que para el próximo ciclo estarían contabilizando el plazo para alcanzar la elegibilidad. </t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Monitorear proceso de elegibilidad.</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1088,6 +1135,8 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1153,6 +1202,16 @@
           <t>Clasificación Validada</t>
         </is>
       </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Comentarios de simulación PMR</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Plan Acción 2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1198,6 +1257,16 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>Satisfactorio</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>No se advierten problemas para mantener la clasificación (operación en cierre)</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1462,6 +1531,8 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1527,6 +1598,16 @@
           <t>Clasificación Validada</t>
         </is>
       </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Comentarios de simulación PMR</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Plan Acción 2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1565,6 +1646,16 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>Satisfactorio</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>No se anticipa riesgo de cambio de clasificación en 2026. Para mantener el indicador de desembolsos en satisfactorio sólo necesita desembolsar $9m en 2026 ($21,6m planeados). Riesgo medio de que SPI y CPI pasen a alerta en función de los gastos realmente reportados para 2026, pero los desembolsos, SPI(a) y CPI(a) mantendrían la operación en satisfactorio.</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Asegurar un desembolso de al menos $9m en 2026. Monitorear avance financiero de intercambios y Taras la Lima para evaluar impacto de metas físicas y financieras en 2027.</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1813,6 +1904,8 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1878,6 +1971,16 @@
           <t>Clasificación Validada</t>
         </is>
       </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Comentarios de simulación PMR</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Plan Acción 2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1916,6 +2019,16 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>Satisfactorio</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>El indicador de desembolsos requiere que se desmbolse el total planeado para 2026 ($20,2m) para mantenerse en alerta (requiere cerca de $35m para pasar a satisfactorio). El SPI probablemente pasará a alerta en 2026 y el SPI(a) requiere ejecutar alrededor de $8m en punta sur para mantenerse satisfactorio. Combinación de desembolsos y SPI en alerta + SPI(a), CPI y CPI(a) en satisfactorio mantendrían la operación en satisfactorio.</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Asegurar al menos la meta de desembolsos de la operación ($20,2m) y garantizar que gastos de punta sur + obras complementarias de punta norte superen los $8m (80% de lo planeado).</t>
         </is>
       </c>
     </row>
@@ -1975,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1989,6 +2102,8 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2054,6 +2169,16 @@
           <t>Clasificación Validada</t>
         </is>
       </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Comentarios de simulación PMR</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Plan Acción 2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2096,6 +2221,16 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>Satisfactorio</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>El indicador de desembolsos se mantendrá en satisfactorio, aun sin desembolsos adicionales. Indicadores SPI(a) y CPI(a) dependen de la finalización de obras planeadas para el 2026. (la operación ya finalizó las obras requeridas para el año y superará las metas físicas, pero como el simulador de la operación tiene errores, es difícil determinar exactamente el impacto de superar las metas).</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Asegurar la finalización de al menos 4 delegaciones policiales y 1 centro cívico en 2026.</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2307,6 +2442,8 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2372,6 +2509,16 @@
           <t>Clasificación Validada</t>
         </is>
       </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Comentarios de simulación PMR</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Plan Acción 2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2410,6 +2557,16 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>Problema</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>El indicador de desembolsos se mantendrá en satisfactorio, aun sin desembolsos adicionales. Indicadores SPI(a), CPI y CPI(a) dependen en gran medida del avance en los procesos de regularización y podrían pasar a satisfactorio si se logra la meta de 60.000 procesos en 2026. Lo anterior es cierto siempre que el avance financiero de CCP Upala y Unidad de refugio sea al menos un 50% de lo planificado. A futuro, la operación se podría beneficiar de la eliminación de productos que no se van a ejecutar y se acordaron en el taller de arranque.</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Monitorear e impulsar la ejecución de los procesos de regularización para alcanzar la meta de 60.000 procesos completados en 2026. Seguimiento al avance de CCP Upala y Unidad de Refugio.</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2503,6 +2660,8 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2568,6 +2727,16 @@
           <t>Clasificación Validada</t>
         </is>
       </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Comentarios de simulación PMR</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Plan Acción 2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2613,6 +2782,16 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>Satisfactorio</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>No se advierten problemas para mantener la clasificación (operación en cierre)</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -2970,7 +3149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2984,6 +3163,8 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -3049,6 +3230,16 @@
           <t>Clasificación Validada</t>
         </is>
       </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Comentarios de simulación PMR</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Plan Acción 2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3069,6 +3260,16 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>Satisfactorio</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Actualmente esperando ratificación. Considerando un proceso de firma de contrato inusual, se recomienda cambiar la clasificación a satisfactorio. El sistema seguirá clasificandolo como alerta automáticamente hasta que obtenga la ratificación.</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Monitorear proceso de ratificación</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3122,6 +3323,8 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -3187,11 +3390,21 @@
           <t>Clasificación Validada</t>
         </is>
       </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Comentarios de simulación PMR</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Plan Acción 2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ciclo I-2026</t>
+          <t>Segundo período enero-diciembre 2025</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -3202,6 +3415,16 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>No indica</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Actualmente esperando ratificación. La operación no muestra clasificación ni gráfica de conteo de días hasta efectividad.</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Monitorear proceso de ratificación</t>
         </is>
       </c>
     </row>
